--- a/output/pdf_financials_xlsx/BTCW.xlsx
+++ b/output/pdf_financials_xlsx/BTCW.xlsx
@@ -431,6 +431,14 @@
   </sheetPr>
   <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/BTCW.xlsx
+++ b/output/pdf_financials_xlsx/BTCW.xlsx
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.006064</v>
+        <v>-0.006064</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.119026</v>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.006064</v>
+        <v>-0.006064</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.119026</v>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.006064</v>
+        <v>-0.006064</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.119026</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.006064</v>
+        <v>-0.006064</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.119026</v>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.006064</v>
+        <v>-0.006064</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.119026</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -26934,7 +26934,7 @@
         </is>
       </c>
       <c r="E406" s="5" t="n">
-        <v>0.006064</v>
+        <v>-0.006064</v>
       </c>
       <c r="F406" s="5" t="n">
         <v>-0.119026</v>

--- a/output/pdf_financials_xlsx/BTCW.xlsx
+++ b/output/pdf_financials_xlsx/BTCW.xlsx
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.006064</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.119642</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>5.501393</v>
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.006064</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.119642</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>1.791326</v>
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000616</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004051</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1285,10 +1285,10 @@
         <v>-0.006064</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.119026</v>
+        <v>-0.119642</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.417489</v>
+        <v>-2.42154</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-14.131419</v>
@@ -1347,10 +1347,10 @@
         <v>-0.006064</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.119026</v>
+        <v>-0.119642</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.417489</v>
+        <v>-2.42154</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-14.131419</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-4.651648888596244</v>
+        <v>-4.659443682966645</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-14.18635423815182</v>
@@ -1489,22 +1489,22 @@
         <v>0.277637</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.242649</v>
+        <v>4.054551</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.799849</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.946525</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.668922</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.875766</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.139299</v>
       </c>
     </row>
     <row r="35">
@@ -1551,22 +1551,22 @@
         <v>0.277637</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.242649</v>
+        <v>4.054551</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.799849</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.946525</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.668922</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.875766</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.139299</v>
       </c>
     </row>
     <row r="37">
@@ -1923,22 +1923,22 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.594116</v>
+        <v>0.782214</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14.072621</v>
+        <v>9.272772</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10.267734</v>
+        <v>6.321209</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12.494572</v>
+        <v>10.82565</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>25.476073</v>
+        <v>22.600307</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>28.222919</v>
+        <v>25.08362</v>
       </c>
     </row>
     <row r="49">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E405" s="5" t="n">

--- a/output/pdf_financials_xlsx/BTCW.xlsx
+++ b/output/pdf_financials_xlsx/BTCW.xlsx
@@ -3928,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.078204</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.005527</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -14154,7 +14154,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -15762,7 +15766,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BTCW.xlsx
+++ b/output/pdf_financials_xlsx/BTCW.xlsx
@@ -2536,16 +2536,16 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.559783</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.579435</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.40286</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.262478</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.100292</v>
       </c>
     </row>
     <row r="111">
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.012365</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -4043,13 +4043,13 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.021967</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.03698</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.567507</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -10846,7 +10846,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -11830,7 +11834,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -12418,7 +12426,11 @@
           <t>Shares issued pursuant to private placement</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -15990,7 +16002,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
